--- a/hw06/excel/test-summary.xlsx
+++ b/hw06/excel/test-summary.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HW06 summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HW06 summary'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HW06 summary'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -434,7 +434,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +473,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Expected FAIL</t>
         </is>
       </c>
@@ -507,7 +525,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -544,6 +577,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
@@ -581,12 +629,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/hw06/excel/test-summary.xlsx
+++ b/hw06/excel/test-summary.xlsx
@@ -525,22 +525,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
